--- a/Container_cost/container_cost.xlsx
+++ b/Container_cost/container_cost.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gtvault-my.sharepoint.com/personal/lcalimlim3_gatech_edu/Documents/Documents/GitHub/ASE6002PEK/Container_cost/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="443" documentId="8_{AE6CABA5-0A59-47A1-890C-095979F6CA6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FA5FF00D-CCF5-436B-917F-D987C3B13DDC}"/>
+  <xr:revisionPtr revIDLastSave="458" documentId="8_{AE6CABA5-0A59-47A1-890C-095979F6CA6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4417E85A-AE21-4103-AF3D-DF9D335E6362}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4A5F281B-5340-485A-8C03-B3650AC26870}"/>
+    <workbookView xWindow="6345" yWindow="1125" windowWidth="21570" windowHeight="11295" xr2:uid="{4A5F281B-5340-485A-8C03-B3650AC26870}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/Container_cost/container_cost.xlsx
+++ b/Container_cost/container_cost.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/07531a99d7244c5b/Documents/GitHub/ASE6002PEK/Container_cost/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="13572" documentId="8_{AE6CABA5-0A59-47A1-890C-095979F6CA6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F4EE0817-90DD-4F34-8776-8D32010D57BB}"/>
+  <xr:revisionPtr revIDLastSave="40132" documentId="8_{AE6CABA5-0A59-47A1-890C-095979F6CA6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4F67BA72-9448-46B3-8468-5AB9E5F30D07}"/>
   <bookViews>
     <workbookView xWindow="9105" yWindow="5325" windowWidth="38700" windowHeight="15345" xr2:uid="{4A5F281B-5340-485A-8C03-B3650AC26870}"/>
   </bookViews>
@@ -625,14 +625,14 @@
         <v>4</v>
       </c>
       <c r="C4">
-        <v>50.000450000000001</v>
+        <v>25</v>
       </c>
       <c r="D4" t="s">
         <v>11</v>
       </c>
       <c r="E4">
         <f>C4*10</f>
-        <v>500.00450000000001</v>
+        <v>250</v>
       </c>
       <c r="I4" t="s">
         <v>22</v>
@@ -687,7 +687,7 @@
       </c>
       <c r="B11" s="4">
         <f>((2*PI()*((E5/2)+C7)*E4) + (PI()*((E5/2)+C7)^2))*C6</f>
-        <v>145287.93514536787</v>
+        <v>77899.559756943228</v>
       </c>
       <c r="C11" t="s">
         <v>12</v>
@@ -699,7 +699,7 @@
       </c>
       <c r="B12" s="4">
         <f>((2*PI()*(E5/2)*E4) + (PI()*(E5/2)^2))*C6</f>
-        <v>139311.16554889505</v>
+        <v>74514.650752332906</v>
       </c>
       <c r="C12" t="s">
         <v>12</v>
@@ -723,7 +723,7 @@
       </c>
       <c r="B15" s="4">
         <f>SUM(B11:B13)</f>
-        <v>284768.74669755675</v>
+        <v>152583.85651257</v>
       </c>
       <c r="C15" t="s">
         <v>12</v>
@@ -735,7 +735,7 @@
       </c>
       <c r="B16" s="3">
         <f>(C3*B15)</f>
-        <v>2.278149973580454</v>
+        <v>1.2206708521005598</v>
       </c>
       <c r="C16" t="s">
         <v>18</v>
@@ -747,7 +747,7 @@
       </c>
       <c r="B17" s="2">
         <f>B16*C2</f>
-        <v>6.3788199260252707</v>
+        <v>3.4178783858815671</v>
       </c>
       <c r="C17" t="s">
         <v>26</v>
@@ -759,7 +759,7 @@
       </c>
       <c r="B19" s="5">
         <f>B17 + SUM(J3:J9)</f>
-        <v>8.3788199260252707</v>
+        <v>5.4178783858815667</v>
       </c>
       <c r="C19" t="s">
         <v>26</v>

--- a/Container_cost/container_cost.xlsx
+++ b/Container_cost/container_cost.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/07531a99d7244c5b/Documents/GitHub/ASE6002PEK/Container_cost/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gtvault-my.sharepoint.com/personal/lcalimlim3_gatech_edu/Documents/Documents/GitHub/ASE6002PEK/Container_cost/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="993" documentId="8_{AE6CABA5-0A59-47A1-890C-095979F6CA6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1530B2C1-BF5C-4CE0-B0F5-10C493515CF5}"/>
+  <xr:revisionPtr revIDLastSave="1005" documentId="8_{AE6CABA5-0A59-47A1-890C-095979F6CA6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7E2DCCFF-3052-462F-AF1E-54AA04AAEBF0}"/>
   <bookViews>
-    <workbookView xWindow="9105" yWindow="5325" windowWidth="38700" windowHeight="15345" xr2:uid="{4A5F281B-5340-485A-8C03-B3650AC26870}"/>
+    <workbookView xWindow="6795" yWindow="30" windowWidth="21570" windowHeight="11295" xr2:uid="{4A5F281B-5340-485A-8C03-B3650AC26870}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -22,6 +22,7 @@
     <definedName name="container_material_density">Sheet1!$C$3</definedName>
     <definedName name="container_raw_material_cost">Sheet1!$C$2</definedName>
     <definedName name="container_wall_thickness">Sheet1!$C$6</definedName>
+    <definedName name="UNC_Cont_Cost">Sheet1!$B$23</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -44,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="36">
   <si>
     <t>material cost</t>
   </si>
@@ -143,6 +144,15 @@
   </si>
   <si>
     <t>container diameter</t>
+  </si>
+  <si>
+    <t>Uncertainty</t>
+  </si>
+  <si>
+    <t>UNC_Cont_Cost</t>
+  </si>
+  <si>
+    <t>%Cost Fluctuation</t>
   </si>
 </sst>
 </file>
@@ -222,6 +232,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -541,7 +555,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4B30057-F495-4BF6-AE09-0A4BFD6BF4A4}">
-  <dimension ref="A1:J19"/>
+  <dimension ref="A1:J23"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26.7109375" customWidth="1"/>
@@ -621,14 +635,14 @@
         <v>4</v>
       </c>
       <c r="C4">
-        <v>0.58874952899999999</v>
+        <v>0.23549999999999999</v>
       </c>
       <c r="D4" t="s">
         <v>11</v>
       </c>
       <c r="E4">
         <f>C4*10</f>
-        <v>5.8874952900000004</v>
+        <v>2.355</v>
       </c>
       <c r="I4" t="s">
         <v>22</v>
@@ -645,14 +659,14 @@
         <v>4</v>
       </c>
       <c r="C5">
-        <v>0.58874952899999999</v>
+        <v>0.23549999999999999</v>
       </c>
       <c r="D5" t="s">
         <v>11</v>
       </c>
       <c r="E5">
         <f>C5*10</f>
-        <v>5.8874952900000004</v>
+        <v>2.355</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
@@ -683,7 +697,7 @@
       </c>
       <c r="B11" s="4">
         <f>((2*PI()*((E5/2)+C7)*E4) + (PI()*((E5/2)+C7)^2))*C6</f>
-        <v>181.97248104013818</v>
+        <v>64.151768681509026</v>
       </c>
       <c r="C11" t="s">
         <v>12</v>
@@ -695,7 +709,7 @@
       </c>
       <c r="B12" s="4">
         <f>((2*PI()*(E5/2)*E4) + (PI()*(E5/2)^2))*C6</f>
-        <v>74.865843246881553</v>
+        <v>11.978554085179917</v>
       </c>
       <c r="C12" t="s">
         <v>12</v>
@@ -707,7 +721,7 @@
       </c>
       <c r="B13" s="4">
         <f>(PI()*(((C5/2)+C7)^2)) - (PI()*(C5/2)^2)</f>
-        <v>33.823167467640694</v>
+        <v>30.493869092069328</v>
       </c>
       <c r="C13" t="s">
         <v>12</v>
@@ -719,7 +733,7 @@
       </c>
       <c r="B15" s="4">
         <f>SUM(B11:B13)</f>
-        <v>290.66149175466046</v>
+        <v>106.62419185875828</v>
       </c>
       <c r="C15" t="s">
         <v>12</v>
@@ -731,7 +745,7 @@
       </c>
       <c r="B16" s="3">
         <f>(C3*B15)</f>
-        <v>2.3252919340372834E-3</v>
+        <v>8.5299353487006623E-4</v>
       </c>
       <c r="C16" t="s">
         <v>18</v>
@@ -743,7 +757,7 @@
       </c>
       <c r="B17" s="2">
         <f>B16*C2</f>
-        <v>6.5108174153043936E-3</v>
+        <v>2.3883818976361852E-3</v>
       </c>
       <c r="C17" t="s">
         <v>26</v>
@@ -754,11 +768,27 @@
         <v>25</v>
       </c>
       <c r="B19" s="5">
-        <f>B17 + SUM(J3:J9)</f>
-        <v>2.0065108174153043</v>
+        <f>(B17 + SUM(J3:J9))*B23</f>
+        <v>2.002388381897636</v>
       </c>
       <c r="C19" t="s">
         <v>26</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>34</v>
+      </c>
+      <c r="B23">
+        <v>1</v>
+      </c>
+      <c r="C23" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>

--- a/Container_cost/container_cost.xlsx
+++ b/Container_cost/container_cost.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gtvault-my.sharepoint.com/personal/lcalimlim3_gatech_edu/Documents/Documents/GitHub/ASE6002PEK/Container_cost/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1005" documentId="8_{AE6CABA5-0A59-47A1-890C-095979F6CA6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7E2DCCFF-3052-462F-AF1E-54AA04AAEBF0}"/>
+  <xr:revisionPtr revIDLastSave="1011" documentId="8_{AE6CABA5-0A59-47A1-890C-095979F6CA6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CEDC6CA2-E4B1-4090-8EEA-15C9ABA3C8B4}"/>
   <bookViews>
-    <workbookView xWindow="6795" yWindow="30" windowWidth="21570" windowHeight="11295" xr2:uid="{4A5F281B-5340-485A-8C03-B3650AC26870}"/>
+    <workbookView xWindow="6255" yWindow="420" windowWidth="21570" windowHeight="11295" xr2:uid="{4A5F281B-5340-485A-8C03-B3650AC26870}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/Container_cost/container_cost.xlsx
+++ b/Container_cost/container_cost.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gtvault-my.sharepoint.com/personal/lcalimlim3_gatech_edu/Documents/Documents/GitHub/ASE6002PEK/Container_cost/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/07531a99d7244c5b/Documents/GitHub/ASE6002PEK/Container_cost/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1011" documentId="8_{AE6CABA5-0A59-47A1-890C-095979F6CA6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CEDC6CA2-E4B1-4090-8EEA-15C9ABA3C8B4}"/>
+  <xr:revisionPtr revIDLastSave="47136" documentId="121_{80702A45-CA11-4E03-8884-34D46572A048}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F7493337-A589-411D-9255-C11C946AD1BD}"/>
   <bookViews>
-    <workbookView xWindow="6255" yWindow="420" windowWidth="21570" windowHeight="11295" xr2:uid="{4A5F281B-5340-485A-8C03-B3650AC26870}"/>
+    <workbookView xWindow="9105" yWindow="5325" windowWidth="38700" windowHeight="15345" xr2:uid="{4A5F281B-5340-485A-8C03-B3650AC26870}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -769,7 +769,7 @@
       </c>
       <c r="B19" s="5">
         <f>(B17 + SUM(J3:J9))*B23</f>
-        <v>2.002388381897636</v>
+        <v>2.0010872535900712</v>
       </c>
       <c r="C19" t="s">
         <v>26</v>
@@ -785,7 +785,7 @@
         <v>34</v>
       </c>
       <c r="B23">
-        <v>1</v>
+        <v>0.99935021181738404</v>
       </c>
       <c r="C23" t="s">
         <v>35</v>

--- a/Container_cost/container_cost.xlsx
+++ b/Container_cost/container_cost.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/07531a99d7244c5b/Documents/GitHub/ASE6002PEK/Container_cost/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="47136" documentId="121_{80702A45-CA11-4E03-8884-34D46572A048}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F7493337-A589-411D-9255-C11C946AD1BD}"/>
+  <xr:revisionPtr revIDLastSave="51767" documentId="121_{80702A45-CA11-4E03-8884-34D46572A048}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8DD83BE1-F787-4957-9859-52F792D5CA90}"/>
   <bookViews>
     <workbookView xWindow="9105" yWindow="5325" windowWidth="38700" windowHeight="15345" xr2:uid="{4A5F281B-5340-485A-8C03-B3650AC26870}"/>
   </bookViews>
@@ -24,7 +24,7 @@
     <definedName name="container_wall_thickness">Sheet1!$C$6</definedName>
     <definedName name="UNC_Cont_Cost">Sheet1!$B$23</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" calcMode="manual"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -769,7 +769,7 @@
       </c>
       <c r="B19" s="5">
         <f>(B17 + SUM(J3:J9))*B23</f>
-        <v>2.0010872535900712</v>
+        <v>1.9959011452442292</v>
       </c>
       <c r="C19" t="s">
         <v>26</v>
@@ -785,7 +785,7 @@
         <v>34</v>
       </c>
       <c r="B23">
-        <v>0.99935021181738404</v>
+        <v>0.99676025055276296</v>
       </c>
       <c r="C23" t="s">
         <v>35</v>

--- a/Container_cost/container_cost.xlsx
+++ b/Container_cost/container_cost.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/07531a99d7244c5b/Documents/GitHub/ASE6002PEK/Container_cost/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="51767" documentId="121_{80702A45-CA11-4E03-8884-34D46572A048}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8DD83BE1-F787-4957-9859-52F792D5CA90}"/>
+  <xr:revisionPtr revIDLastSave="51947" documentId="121_{80702A45-CA11-4E03-8884-34D46572A048}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D9542DAB-64D1-447E-9EF2-FDA56CA8D5FA}"/>
   <bookViews>
     <workbookView xWindow="9105" yWindow="5325" windowWidth="38700" windowHeight="15345" xr2:uid="{4A5F281B-5340-485A-8C03-B3650AC26870}"/>
   </bookViews>
@@ -769,7 +769,7 @@
       </c>
       <c r="B19" s="5">
         <f>(B17 + SUM(J3:J9))*B23</f>
-        <v>1.9959011452442292</v>
+        <v>2.0023765057170571</v>
       </c>
       <c r="C19" t="s">
         <v>26</v>
@@ -785,7 +785,7 @@
         <v>34</v>
       </c>
       <c r="B23">
-        <v>0.99676025055276296</v>
+        <v>0.99999406899246601</v>
       </c>
       <c r="C23" t="s">
         <v>35</v>

--- a/Container_cost/container_cost.xlsx
+++ b/Container_cost/container_cost.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/07531a99d7244c5b/Documents/GitHub/ASE6002PEK/Container_cost/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="51947" documentId="121_{80702A45-CA11-4E03-8884-34D46572A048}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D9542DAB-64D1-447E-9EF2-FDA56CA8D5FA}"/>
+  <xr:revisionPtr revIDLastSave="53891" documentId="121_{80702A45-CA11-4E03-8884-34D46572A048}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8D6D261D-572D-455B-9F83-7CD3B9D80F4D}"/>
   <bookViews>
     <workbookView xWindow="9105" yWindow="5325" windowWidth="38700" windowHeight="15345" xr2:uid="{4A5F281B-5340-485A-8C03-B3650AC26870}"/>
   </bookViews>
@@ -769,7 +769,7 @@
       </c>
       <c r="B19" s="5">
         <f>(B17 + SUM(J3:J9))*B23</f>
-        <v>2.0023765057170571</v>
+        <v>1.9978681616896079</v>
       </c>
       <c r="C19" t="s">
         <v>26</v>
@@ -785,7 +785,7 @@
         <v>34</v>
       </c>
       <c r="B23">
-        <v>0.99999406899246601</v>
+        <v>0.99774258567973495</v>
       </c>
       <c r="C23" t="s">
         <v>35</v>

--- a/Container_cost/container_cost.xlsx
+++ b/Container_cost/container_cost.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/07531a99d7244c5b/Documents/GitHub/ASE6002PEK/Container_cost/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="53891" documentId="121_{80702A45-CA11-4E03-8884-34D46572A048}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8D6D261D-572D-455B-9F83-7CD3B9D80F4D}"/>
+  <xr:revisionPtr revIDLastSave="59891" documentId="121_{80702A45-CA11-4E03-8884-34D46572A048}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8DA3B3F7-6E0D-4AAB-A2B9-E89C766BCCC2}"/>
   <bookViews>
     <workbookView xWindow="9105" yWindow="5325" windowWidth="38700" windowHeight="15345" xr2:uid="{4A5F281B-5340-485A-8C03-B3650AC26870}"/>
   </bookViews>
@@ -769,7 +769,7 @@
       </c>
       <c r="B19" s="5">
         <f>(B17 + SUM(J3:J9))*B23</f>
-        <v>1.9978681616896079</v>
+        <v>1.9969953477374027</v>
       </c>
       <c r="C19" t="s">
         <v>26</v>
@@ -785,7 +785,7 @@
         <v>34</v>
       </c>
       <c r="B23">
-        <v>0.99774258567973495</v>
+        <v>0.99730669923527904</v>
       </c>
       <c r="C23" t="s">
         <v>35</v>
